--- a/output/Tables/2019/Monte Carlo/HIA_per_sex_Rubin.xlsx
+++ b/output/Tables/2019/Monte Carlo/HIA_per_sex_Rubin.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>24501.466</v>
+        <v>24487.753</v>
       </c>
       <c r="D2">
-        <v>22815.761</v>
+        <v>22820.689</v>
       </c>
       <c r="E2">
-        <v>26151.935</v>
+        <v>26154.817</v>
       </c>
       <c r="F2">
-        <v>286625.785</v>
+        <v>286609.01</v>
       </c>
       <c r="G2">
-        <v>275247.701</v>
+        <v>275303.541</v>
       </c>
       <c r="H2">
-        <v>297903.434</v>
+        <v>297914.48</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>38145221646.419</v>
+        <v>38118998395.105</v>
       </c>
       <c r="M2">
-        <v>36622738905.928</v>
+        <v>36615370997.826</v>
       </c>
       <c r="N2">
-        <v>39602385181.33</v>
+        <v>39622625792.384</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>34082.813</v>
+        <v>34005.91</v>
       </c>
       <c r="D3">
-        <v>31633.918</v>
+        <v>31544.917</v>
       </c>
       <c r="E3">
-        <v>36481.964</v>
+        <v>36466.904</v>
       </c>
       <c r="F3">
-        <v>318411.653</v>
+        <v>318217.053</v>
       </c>
       <c r="G3">
-        <v>302916.308</v>
+        <v>302423.94</v>
       </c>
       <c r="H3">
-        <v>334997.256</v>
+        <v>334010.165</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>42425855022.044</v>
+        <v>42322867998.438</v>
       </c>
       <c r="M3">
-        <v>40260711406.757</v>
+        <v>40222384014.252</v>
       </c>
       <c r="N3">
-        <v>44477807958.925</v>
+        <v>44423351982.624</v>
       </c>
     </row>
     <row r="4">
@@ -534,40 +534,40 @@
         </is>
       </c>
       <c r="C4">
-        <v>18838.682</v>
+        <v>18793.13</v>
       </c>
       <c r="D4">
-        <v>17772.288</v>
+        <v>17708.044</v>
       </c>
       <c r="E4">
-        <v>19904.139</v>
+        <v>19878.216</v>
       </c>
       <c r="F4">
-        <v>19092.621</v>
+        <v>19064.596</v>
       </c>
       <c r="G4">
-        <v>18173.586</v>
+        <v>18072.635</v>
       </c>
       <c r="H4">
-        <v>20104.145</v>
+        <v>20056.556</v>
       </c>
       <c r="I4">
-        <v>1048900281.887</v>
+        <v>1046814931.246</v>
       </c>
       <c r="J4">
-        <v>990652324.595</v>
+        <v>986373456.046</v>
       </c>
       <c r="K4">
-        <v>1112121965.608</v>
+        <v>1107256406.446</v>
       </c>
       <c r="L4">
-        <v>2536928606.133</v>
+        <v>2535591201.555</v>
       </c>
       <c r="M4">
-        <v>2408721112.171</v>
+        <v>2403660460.552</v>
       </c>
       <c r="N4">
-        <v>2664096207.17</v>
+        <v>2667521942.558</v>
       </c>
     </row>
     <row r="5">
@@ -582,40 +582,40 @@
         </is>
       </c>
       <c r="C5">
-        <v>21343.115</v>
+        <v>21316.518</v>
       </c>
       <c r="D5">
-        <v>19780.512</v>
+        <v>19851.276</v>
       </c>
       <c r="E5">
-        <v>22801.946</v>
+        <v>22781.761</v>
       </c>
       <c r="F5">
-        <v>16845.125</v>
+        <v>16835.791</v>
       </c>
       <c r="G5">
-        <v>15805.175</v>
+        <v>15724.773</v>
       </c>
       <c r="H5">
-        <v>17989.622</v>
+        <v>17946.81</v>
       </c>
       <c r="I5">
-        <v>1186485813.309</v>
+        <v>1187372706.17</v>
       </c>
       <c r="J5">
-        <v>1106894051.331</v>
+        <v>1105755785.569</v>
       </c>
       <c r="K5">
-        <v>1266323320.719</v>
+        <v>1268989626.771</v>
       </c>
       <c r="L5">
-        <v>2240089797.983</v>
+        <v>2239160226.503</v>
       </c>
       <c r="M5">
-        <v>2096455522.738</v>
+        <v>2091394753.645</v>
       </c>
       <c r="N5">
-        <v>2385282351.618</v>
+        <v>2386925699.362</v>
       </c>
     </row>
     <row r="6">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>19966.669</v>
+        <v>20090.019</v>
       </c>
       <c r="D6">
-        <v>18819.269</v>
+        <v>18849.234</v>
       </c>
       <c r="E6">
-        <v>21158.775</v>
+        <v>21330.803</v>
       </c>
       <c r="F6">
-        <v>35649.279</v>
+        <v>36051.965</v>
       </c>
       <c r="G6">
-        <v>33232.543</v>
+        <v>33409.445</v>
       </c>
       <c r="H6">
-        <v>38232.672</v>
+        <v>38694.485</v>
       </c>
       <c r="I6">
-        <v>295640477.363</v>
+        <v>297472908.637</v>
       </c>
       <c r="J6">
-        <v>278341268.95</v>
+        <v>279100610.374</v>
       </c>
       <c r="K6">
-        <v>313271388.443</v>
+        <v>315845206.9</v>
       </c>
       <c r="L6">
-        <v>4743779558.439</v>
+        <v>4794911327.86</v>
       </c>
       <c r="M6">
-        <v>4426837553.204</v>
+        <v>4443456201.657</v>
       </c>
       <c r="N6">
-        <v>5073981091.098</v>
+        <v>5146366454.064</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>11035.363</v>
+        <v>11115.623</v>
       </c>
       <c r="D7">
-        <v>10170.747</v>
+        <v>10221.76</v>
       </c>
       <c r="E7">
-        <v>11990.031</v>
+        <v>12009.486</v>
       </c>
       <c r="F7">
-        <v>10922.769</v>
+        <v>10909.968</v>
       </c>
       <c r="G7">
-        <v>10044.827</v>
+        <v>10057.228</v>
       </c>
       <c r="H7">
-        <v>11732.86</v>
+        <v>11762.709</v>
       </c>
       <c r="I7">
-        <v>163546185.905</v>
+        <v>164589024.811</v>
       </c>
       <c r="J7">
-        <v>150351926.554</v>
+        <v>151353593.952</v>
       </c>
       <c r="K7">
-        <v>177913341.746</v>
+        <v>177824455.671</v>
       </c>
       <c r="L7">
-        <v>1452025090.843</v>
+        <v>1451025758.955</v>
       </c>
       <c r="M7">
-        <v>1344888266.954</v>
+        <v>1337611264.452</v>
       </c>
       <c r="N7">
-        <v>1567049951.587</v>
+        <v>1564440253.457</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>3023.994</v>
+        <v>3028.153</v>
       </c>
       <c r="D8">
-        <v>2827.507</v>
+        <v>2834.347</v>
       </c>
       <c r="E8">
-        <v>3220.825</v>
+        <v>3221.959</v>
       </c>
       <c r="F8">
-        <v>6385.212</v>
+        <v>6385.386</v>
       </c>
       <c r="G8">
-        <v>5978.767</v>
+        <v>5955.272</v>
       </c>
       <c r="H8">
-        <v>6788.226</v>
+        <v>6815.499</v>
       </c>
       <c r="I8">
-        <v>227438193.209</v>
+        <v>227720107.755</v>
       </c>
       <c r="J8">
-        <v>212859378.865</v>
+        <v>213145706.218</v>
       </c>
       <c r="K8">
-        <v>242697287.815</v>
+        <v>242294509.291</v>
       </c>
       <c r="L8">
-        <v>847059216.785</v>
+        <v>849256278.643</v>
       </c>
       <c r="M8">
-        <v>794058336.105</v>
+        <v>792051182.29</v>
       </c>
       <c r="N8">
-        <v>904873224.785</v>
+        <v>906461374.997</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>3372.537</v>
+        <v>3375.744</v>
       </c>
       <c r="D9">
-        <v>3115.013</v>
+        <v>3119.553</v>
       </c>
       <c r="E9">
-        <v>3623.25</v>
+        <v>3631.936</v>
       </c>
       <c r="F9">
-        <v>6128.074</v>
+        <v>6129.424</v>
       </c>
       <c r="G9">
-        <v>5597.972</v>
+        <v>5640.514</v>
       </c>
       <c r="H9">
-        <v>6611.991</v>
+        <v>6618.334</v>
       </c>
       <c r="I9">
-        <v>253852727.306</v>
+        <v>253859346.552</v>
       </c>
       <c r="J9">
-        <v>235009756.465</v>
+        <v>234593508.067</v>
       </c>
       <c r="K9">
-        <v>272265197.184</v>
+        <v>273125185.037</v>
       </c>
       <c r="L9">
-        <v>815612801.477</v>
+        <v>815213396.209</v>
       </c>
       <c r="M9">
-        <v>746687614.2690001</v>
+        <v>750188398.984</v>
       </c>
       <c r="N9">
-        <v>882125792.076</v>
+        <v>880238393.434</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>8489.784</v>
+        <v>8523.616</v>
       </c>
       <c r="D10">
-        <v>7844.663</v>
+        <v>7851.49</v>
       </c>
       <c r="E10">
-        <v>9198.362999999999</v>
+        <v>9195.741</v>
       </c>
       <c r="F10">
-        <v>16994.91</v>
+        <v>16980.542</v>
       </c>
       <c r="G10">
-        <v>15890.484</v>
+        <v>15905.616</v>
       </c>
       <c r="H10">
-        <v>18058.709</v>
+        <v>18055.468</v>
       </c>
       <c r="I10">
-        <v>143477919.529</v>
+        <v>143529165.787</v>
       </c>
       <c r="J10">
-        <v>131688593.465</v>
+        <v>132211247.659</v>
       </c>
       <c r="K10">
-        <v>154924929.985</v>
+        <v>154847083.914</v>
       </c>
       <c r="L10">
-        <v>2258926607.44</v>
+        <v>2258412067.596</v>
       </c>
       <c r="M10">
-        <v>2121747288.128</v>
+        <v>2115446922.575</v>
       </c>
       <c r="N10">
-        <v>2396018492.799</v>
+        <v>2401377212.616</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>5462.105</v>
+        <v>5412.333</v>
       </c>
       <c r="D11">
-        <v>4905.375</v>
+        <v>4866.713</v>
       </c>
       <c r="E11">
-        <v>5995.378</v>
+        <v>5957.952</v>
       </c>
       <c r="F11">
-        <v>6275.232</v>
+        <v>6261.47</v>
       </c>
       <c r="G11">
-        <v>5770.764</v>
+        <v>5763.534</v>
       </c>
       <c r="H11">
-        <v>6780.144</v>
+        <v>6759.406</v>
       </c>
       <c r="I11">
-        <v>91888606.234</v>
+        <v>91138267.605</v>
       </c>
       <c r="J11">
-        <v>82588224.236</v>
+        <v>81950587.87899999</v>
       </c>
       <c r="K11">
-        <v>101550703.813</v>
+        <v>100325947.332</v>
       </c>
       <c r="L11">
-        <v>833367434.553</v>
+        <v>832775510.186</v>
       </c>
       <c r="M11">
-        <v>769491934.258</v>
+        <v>766550046.0880001</v>
       </c>
       <c r="N11">
-        <v>899600646.701</v>
+        <v>899000974.285</v>
       </c>
     </row>
     <row r="12">
@@ -918,22 +918,22 @@
         </is>
       </c>
       <c r="C12">
-        <v>107144.622</v>
+        <v>107147.824</v>
       </c>
       <c r="D12">
-        <v>102075.199</v>
+        <v>101964.588</v>
       </c>
       <c r="E12">
-        <v>112577.42</v>
+        <v>112331.06</v>
       </c>
       <c r="F12">
-        <v>331285.046</v>
+        <v>12489.72</v>
       </c>
       <c r="G12">
-        <v>308326.158</v>
+        <v>11841.301</v>
       </c>
       <c r="H12">
-        <v>353546.031</v>
+        <v>13138.138</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -945,13 +945,13 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>44028816006.772</v>
+        <v>1661132697.607</v>
       </c>
       <c r="M12">
-        <v>41230768731.762</v>
+        <v>1574893070.487</v>
       </c>
       <c r="N12">
-        <v>47042811853.432</v>
+        <v>1747372324.727</v>
       </c>
     </row>
     <row r="13">
@@ -966,22 +966,22 @@
         </is>
       </c>
       <c r="C13">
-        <v>44779.056</v>
+        <v>44780.629</v>
       </c>
       <c r="D13">
-        <v>42270.893</v>
+        <v>42294.58</v>
       </c>
       <c r="E13">
-        <v>47328.53</v>
+        <v>47266.678</v>
       </c>
       <c r="F13">
-        <v>114415.384</v>
+        <v>5021.445</v>
       </c>
       <c r="G13">
-        <v>105996.215</v>
+        <v>4717.324</v>
       </c>
       <c r="H13">
-        <v>123360.287</v>
+        <v>5325.565</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -993,13 +993,13 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>15266441475.213</v>
+        <v>667852139.827</v>
       </c>
       <c r="M13">
-        <v>14165007250.083</v>
+        <v>627404077.473</v>
       </c>
       <c r="N13">
-        <v>16392945161.596</v>
+        <v>708300202.1799999</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/Monte Carlo/HIA_per_sex_Rubin.xlsx
+++ b/output/Tables/2019/Monte Carlo/HIA_per_sex_Rubin.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>24487.753</v>
+        <v>24484.382</v>
       </c>
       <c r="D2">
-        <v>22820.689</v>
+        <v>22817.683</v>
       </c>
       <c r="E2">
-        <v>26154.817</v>
+        <v>26151.082</v>
       </c>
       <c r="F2">
-        <v>286609.01</v>
+        <v>286592.527</v>
       </c>
       <c r="G2">
-        <v>275303.541</v>
+        <v>275289.305</v>
       </c>
       <c r="H2">
-        <v>297914.48</v>
+        <v>297895.748</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>38118998395.105</v>
+        <v>38116806030.764</v>
       </c>
       <c r="M2">
-        <v>36615370997.826</v>
+        <v>36613477616.16</v>
       </c>
       <c r="N2">
-        <v>39622625792.384</v>
+        <v>39620134445.368</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>34005.91</v>
+        <v>34006.945</v>
       </c>
       <c r="D3">
-        <v>31544.917</v>
+        <v>31545.785</v>
       </c>
       <c r="E3">
-        <v>36466.904</v>
+        <v>36468.105</v>
       </c>
       <c r="F3">
-        <v>318217.053</v>
+        <v>318208.661</v>
       </c>
       <c r="G3">
-        <v>302423.94</v>
+        <v>302412.472</v>
       </c>
       <c r="H3">
-        <v>334010.165</v>
+        <v>334004.851</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>42322867998.438</v>
+        <v>42321751970.957</v>
       </c>
       <c r="M3">
-        <v>40222384014.252</v>
+        <v>40220858819.575</v>
       </c>
       <c r="N3">
-        <v>44423351982.624</v>
+        <v>44422645122.339</v>
       </c>
     </row>
     <row r="4">
@@ -534,40 +534,40 @@
         </is>
       </c>
       <c r="C4">
-        <v>18793.13</v>
+        <v>18755.572</v>
       </c>
       <c r="D4">
-        <v>17708.044</v>
+        <v>17670.305</v>
       </c>
       <c r="E4">
-        <v>19878.216</v>
+        <v>19840.838</v>
       </c>
       <c r="F4">
-        <v>19064.596</v>
+        <v>19055.024</v>
       </c>
       <c r="G4">
-        <v>18072.635</v>
+        <v>18062.179</v>
       </c>
       <c r="H4">
-        <v>20056.556</v>
+        <v>20047.87</v>
       </c>
       <c r="I4">
-        <v>1046814931.246</v>
+        <v>1044722848.842</v>
       </c>
       <c r="J4">
-        <v>986373456.046</v>
+        <v>984271316.625</v>
       </c>
       <c r="K4">
-        <v>1107256406.446</v>
+        <v>1105174381.059</v>
       </c>
       <c r="L4">
-        <v>2535591201.555</v>
+        <v>2534318227.983</v>
       </c>
       <c r="M4">
-        <v>2403660460.552</v>
+        <v>2402269786.887</v>
       </c>
       <c r="N4">
-        <v>2667521942.558</v>
+        <v>2666366669.079</v>
       </c>
     </row>
     <row r="5">
@@ -582,40 +582,40 @@
         </is>
       </c>
       <c r="C5">
-        <v>21316.518</v>
+        <v>21386.338</v>
       </c>
       <c r="D5">
-        <v>19851.276</v>
+        <v>19915.95</v>
       </c>
       <c r="E5">
-        <v>22781.761</v>
+        <v>22856.725</v>
       </c>
       <c r="F5">
-        <v>16835.791</v>
+        <v>16874.272</v>
       </c>
       <c r="G5">
-        <v>15724.773</v>
+        <v>15759.75</v>
       </c>
       <c r="H5">
-        <v>17946.81</v>
+        <v>17988.795</v>
       </c>
       <c r="I5">
-        <v>1187372706.17</v>
+        <v>1191261784.668</v>
       </c>
       <c r="J5">
-        <v>1105755785.569</v>
+        <v>1109358249.943</v>
       </c>
       <c r="K5">
-        <v>1268989626.771</v>
+        <v>1273165319.394</v>
       </c>
       <c r="L5">
-        <v>2239160226.503</v>
+        <v>2244278230.873</v>
       </c>
       <c r="M5">
-        <v>2091394753.645</v>
+        <v>2096046728.689</v>
       </c>
       <c r="N5">
-        <v>2386925699.362</v>
+        <v>2392509733.058</v>
       </c>
     </row>
     <row r="6">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>20090.019</v>
+        <v>20118.555</v>
       </c>
       <c r="D6">
-        <v>18849.234</v>
+        <v>18876.184</v>
       </c>
       <c r="E6">
-        <v>21330.803</v>
+        <v>21360.927</v>
       </c>
       <c r="F6">
-        <v>36051.965</v>
+        <v>36182.954</v>
       </c>
       <c r="G6">
-        <v>33409.445</v>
+        <v>33529.201</v>
       </c>
       <c r="H6">
-        <v>38694.485</v>
+        <v>38836.706</v>
       </c>
       <c r="I6">
-        <v>297472908.637</v>
+        <v>297895448.539</v>
       </c>
       <c r="J6">
-        <v>279100610.374</v>
+        <v>279499655.932</v>
       </c>
       <c r="K6">
-        <v>315845206.9</v>
+        <v>316291241.146</v>
       </c>
       <c r="L6">
-        <v>4794911327.86</v>
+        <v>4812332820.065</v>
       </c>
       <c r="M6">
-        <v>4443456201.657</v>
+        <v>4459383783.973</v>
       </c>
       <c r="N6">
-        <v>5146366454.064</v>
+        <v>5165281856.157</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>11115.623</v>
+        <v>11100.139</v>
       </c>
       <c r="D7">
-        <v>10221.76</v>
+        <v>10208.094</v>
       </c>
       <c r="E7">
-        <v>12009.486</v>
+        <v>11992.183</v>
       </c>
       <c r="F7">
-        <v>10909.968</v>
+        <v>10875.367</v>
       </c>
       <c r="G7">
-        <v>10057.228</v>
+        <v>10027.241</v>
       </c>
       <c r="H7">
-        <v>11762.709</v>
+        <v>11723.494</v>
       </c>
       <c r="I7">
-        <v>164589024.811</v>
+        <v>164359754.344</v>
       </c>
       <c r="J7">
-        <v>151353593.952</v>
+        <v>151151252.053</v>
       </c>
       <c r="K7">
-        <v>177824455.671</v>
+        <v>177568256.635</v>
       </c>
       <c r="L7">
-        <v>1451025758.955</v>
+        <v>1446423824.823</v>
       </c>
       <c r="M7">
-        <v>1337611264.452</v>
+        <v>1333623001.666</v>
       </c>
       <c r="N7">
-        <v>1564440253.457</v>
+        <v>1559224647.98</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>3028.153</v>
+        <v>3034.604</v>
       </c>
       <c r="D8">
-        <v>2834.347</v>
+        <v>2840.381</v>
       </c>
       <c r="E8">
-        <v>3221.959</v>
+        <v>3228.826</v>
       </c>
       <c r="F8">
-        <v>6385.386</v>
+        <v>6380.127</v>
       </c>
       <c r="G8">
-        <v>5955.272</v>
+        <v>5951.624</v>
       </c>
       <c r="H8">
-        <v>6815.499</v>
+        <v>6808.63</v>
       </c>
       <c r="I8">
-        <v>227720107.755</v>
+        <v>228205227.588</v>
       </c>
       <c r="J8">
-        <v>213145706.218</v>
+        <v>213599508.011</v>
       </c>
       <c r="K8">
-        <v>242294509.291</v>
+        <v>242810947.165</v>
       </c>
       <c r="L8">
-        <v>849256278.643</v>
+        <v>848556868.044</v>
       </c>
       <c r="M8">
-        <v>792051182.29</v>
+        <v>791565944.791</v>
       </c>
       <c r="N8">
-        <v>906461374.997</v>
+        <v>905547791.2970001</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>3375.744</v>
+        <v>3370.452</v>
       </c>
       <c r="D9">
-        <v>3119.553</v>
+        <v>3115.701</v>
       </c>
       <c r="E9">
-        <v>3631.936</v>
+        <v>3625.202</v>
       </c>
       <c r="F9">
-        <v>6129.424</v>
+        <v>6124.909</v>
       </c>
       <c r="G9">
-        <v>5640.514</v>
+        <v>5639.892</v>
       </c>
       <c r="H9">
-        <v>6618.334</v>
+        <v>6609.926</v>
       </c>
       <c r="I9">
-        <v>253859346.552</v>
+        <v>253461345.501</v>
       </c>
       <c r="J9">
-        <v>234593508.067</v>
+        <v>234303857.073</v>
       </c>
       <c r="K9">
-        <v>273125185.037</v>
+        <v>272618833.928</v>
       </c>
       <c r="L9">
-        <v>815213396.209</v>
+        <v>814612899.642</v>
       </c>
       <c r="M9">
-        <v>750188398.984</v>
+        <v>750105681.215</v>
       </c>
       <c r="N9">
-        <v>880238393.434</v>
+        <v>879120118.069</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>8523.616</v>
+        <v>8521.058999999999</v>
       </c>
       <c r="D10">
-        <v>7851.49</v>
+        <v>7850.549</v>
       </c>
       <c r="E10">
-        <v>9195.741</v>
+        <v>9191.567999999999</v>
       </c>
       <c r="F10">
-        <v>16980.542</v>
+        <v>16973.466</v>
       </c>
       <c r="G10">
-        <v>15905.616</v>
+        <v>15902.145</v>
       </c>
       <c r="H10">
-        <v>18055.468</v>
+        <v>18044.788</v>
       </c>
       <c r="I10">
-        <v>143529165.787</v>
+        <v>143486104.186</v>
       </c>
       <c r="J10">
-        <v>132211247.659</v>
+        <v>132195387.186</v>
       </c>
       <c r="K10">
-        <v>154847083.914</v>
+        <v>154776821.185</v>
       </c>
       <c r="L10">
-        <v>2258412067.596</v>
+        <v>2257471031.039</v>
       </c>
       <c r="M10">
-        <v>2115446922.575</v>
+        <v>2114985283.955</v>
       </c>
       <c r="N10">
-        <v>2401377212.616</v>
+        <v>2399956778.123</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>5412.333</v>
+        <v>5413.138</v>
       </c>
       <c r="D11">
-        <v>4866.713</v>
+        <v>4869.917</v>
       </c>
       <c r="E11">
-        <v>5957.952</v>
+        <v>5956.36</v>
       </c>
       <c r="F11">
-        <v>6261.47</v>
+        <v>6281.876</v>
       </c>
       <c r="G11">
-        <v>5763.534</v>
+        <v>5780.848</v>
       </c>
       <c r="H11">
-        <v>6759.406</v>
+        <v>6782.905</v>
       </c>
       <c r="I11">
-        <v>91138267.605</v>
+        <v>91151836.77</v>
       </c>
       <c r="J11">
-        <v>81950587.87899999</v>
+        <v>82004527.34100001</v>
       </c>
       <c r="K11">
-        <v>100325947.332</v>
+        <v>100299146.198</v>
       </c>
       <c r="L11">
-        <v>832775510.186</v>
+        <v>835489566.4910001</v>
       </c>
       <c r="M11">
-        <v>766550046.0880001</v>
+        <v>768852794.984</v>
       </c>
       <c r="N11">
-        <v>899000974.285</v>
+        <v>902126337.997</v>
       </c>
     </row>
     <row r="12">
@@ -918,22 +918,22 @@
         </is>
       </c>
       <c r="C12">
-        <v>107147.824</v>
+        <v>88817.677</v>
       </c>
       <c r="D12">
-        <v>101964.588</v>
+        <v>84348.64599999999</v>
       </c>
       <c r="E12">
-        <v>112331.06</v>
+        <v>93286.70699999999</v>
       </c>
       <c r="F12">
-        <v>12489.72</v>
+        <v>30403.251</v>
       </c>
       <c r="G12">
-        <v>11841.301</v>
+        <v>28365.659</v>
       </c>
       <c r="H12">
-        <v>13138.138</v>
+        <v>32440.844</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -945,13 +945,13 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>1661132697.607</v>
+        <v>4043632437.721</v>
       </c>
       <c r="M12">
-        <v>1574893070.487</v>
+        <v>3772632666.344</v>
       </c>
       <c r="N12">
-        <v>1747372324.727</v>
+        <v>4314632209.098</v>
       </c>
     </row>
     <row r="13">
@@ -966,22 +966,22 @@
         </is>
       </c>
       <c r="C13">
-        <v>44780.629</v>
+        <v>37149.661</v>
       </c>
       <c r="D13">
-        <v>42294.58</v>
+        <v>34996.105</v>
       </c>
       <c r="E13">
-        <v>47266.678</v>
+        <v>39303.218</v>
       </c>
       <c r="F13">
-        <v>5021.445</v>
+        <v>10613.377</v>
       </c>
       <c r="G13">
-        <v>4717.324</v>
+        <v>9796.397000000001</v>
       </c>
       <c r="H13">
-        <v>5325.565</v>
+        <v>11430.358</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -993,13 +993,13 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>667852139.827</v>
+        <v>1411579177.281</v>
       </c>
       <c r="M13">
-        <v>627404077.473</v>
+        <v>1302920766.586</v>
       </c>
       <c r="N13">
-        <v>708300202.1799999</v>
+        <v>1520237587.975</v>
       </c>
     </row>
   </sheetData>
